--- a/hourly datasets/cap_gen_year21final.xlsx
+++ b/hourly datasets/cap_gen_year21final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1113992423925084</v>
+        <v>0.1099922991640129</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1254454475001058</v>
+        <v>0.1245903538708641</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2368446898926141</v>
+        <v>0.234582653034877</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1490700599357073</v>
+        <v>0.1497308692574472</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2604693023282156</v>
+        <v>0.2597231684214601</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04494109595997438</v>
+        <v>0.04037235188335056</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1563403383524828</v>
+        <v>0.1503646510473634</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02783826860116842</v>
+        <v>0.0219042523036234</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +557,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1392375109936768</v>
+        <v>0.1318965514676363</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01649965745265265</v>
+        <v>0.01048225142366272</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001700272677293911</v>
+        <v>0.0009690270228351216</v>
       </c>
       <c r="D7" t="n">
-        <v>2.879625934947438</v>
+        <v>2.279231618169682</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008800124277461713</v>
+        <v>0.004674473351215604</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01316146255509465</v>
+        <v>0.008582127863249012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01983785235021041</v>
+        <v>0.01238237498407649</v>
       </c>
       <c r="H7" t="n">
-        <v>0.127898899845161</v>
+        <v>0.1204745505876756</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01093051472373631</v>
+        <v>0.0047949996257823</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -603,7 +603,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1223297571162447</v>
+        <v>0.1147872987897952</v>
       </c>
     </row>
     <row r="9">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0121749531417285</v>
+        <v>0.005354538264192019</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -621,7 +621,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.1235741955342369</v>
+        <v>0.1153468374282049</v>
       </c>
     </row>
     <row r="10">
@@ -631,25 +631,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01084051814073153</v>
+        <v>0.004634699302963697</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001058575450541831</v>
+        <v>0.0005019805384454752</v>
       </c>
       <c r="D10" t="n">
-        <v>2.026330108066947</v>
+        <v>1.31814222373769</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003584510644042815</v>
+        <v>0.00101778462807955</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008760414580765916</v>
+        <v>0.003650114073445437</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01292062170069702</v>
+        <v>0.005619284532481997</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1222397605332399</v>
+        <v>0.1146269984669766</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02965607392827552</v>
+        <v>0.02893992749805298</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -667,7 +667,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1410553163207839</v>
+        <v>0.1389322266620658</v>
       </c>
     </row>
     <row r="12">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05657811113143149</v>
+        <v>0.05439636376376</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -685,7 +685,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1679773535239399</v>
+        <v>0.1643886629277729</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07498615613373034</v>
+        <v>0.07168763115979133</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -703,7 +703,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1863853985262387</v>
+        <v>0.1816799303238042</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08489125675829605</v>
+        <v>0.08184471996025694</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -721,7 +721,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1962904991508044</v>
+        <v>0.1918370191242698</v>
       </c>
     </row>
     <row r="15">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09049349916045676</v>
+        <v>0.08722709666190667</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -739,7 +739,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.2018927415529652</v>
+        <v>0.1972193958259195</v>
       </c>
     </row>
     <row r="16">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09522265827235654</v>
+        <v>0.09199864996852229</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -757,7 +757,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.2066219006648649</v>
+        <v>0.2019909491325352</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09864656041426952</v>
+        <v>0.09562710807701701</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.2100458028067779</v>
+        <v>0.2056194072410299</v>
       </c>
     </row>
     <row r="18">
@@ -785,22 +785,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1113992423925084</v>
+        <v>-0.1099922991640129</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00788488177873389</v>
+        <v>0.007475328656340139</v>
       </c>
       <c r="D18" t="n">
-        <v>-23.33541603221571</v>
+        <v>-23.43831166551434</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02595550254954082</v>
+        <v>0.02516238180502941</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1269030552147783</v>
+        <v>-0.1246656641882574</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09589542957023811</v>
+        <v>-0.09531893413976801</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09987356293835122</v>
+        <v>0.09716239785072142</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -821,7 +821,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.2112728053308596</v>
+        <v>0.2071546970147343</v>
       </c>
     </row>
     <row r="20">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1021766204415719</v>
+        <v>0.09959519344057345</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -839,7 +839,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2135758628340803</v>
+        <v>0.2095874926045863</v>
       </c>
     </row>
     <row r="21">
@@ -849,25 +849,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1059495378426912</v>
+        <v>0.1032827074198596</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006285832327742063</v>
+        <v>0.006113417648424865</v>
       </c>
       <c r="D21" t="n">
-        <v>27.93579322505903</v>
+        <v>27.66357091915198</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03486148792792863</v>
+        <v>0.0363941273807872</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09359442412155294</v>
+        <v>0.09126727033739016</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1183046515638294</v>
+        <v>0.1152981445023289</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2173487802351996</v>
+        <v>0.2132750065838725</v>
       </c>
     </row>
     <row r="22">
@@ -877,25 +877,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1101130185115464</v>
+        <v>0.1068995960763939</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006323449521945069</v>
+        <v>0.006169666318318684</v>
       </c>
       <c r="D22" t="n">
-        <v>29.17957887082748</v>
+        <v>28.89223891325086</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03421171292818506</v>
+        <v>0.03646600785838826</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09767520931049724</v>
+        <v>0.09476903545491545</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1225508277125959</v>
+        <v>0.1190301566978724</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2215122609040548</v>
+        <v>0.2168918952404068</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1158468035174292</v>
+        <v>0.1127150527305676</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +913,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2272460459099376</v>
+        <v>0.2227073518945805</v>
       </c>
     </row>
     <row r="24">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1176795602584984</v>
+        <v>0.1157665267859361</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -931,7 +931,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2290788026510067</v>
+        <v>0.2257588259499489</v>
       </c>
     </row>
     <row r="25">
@@ -941,25 +941,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1204609444041502</v>
+        <v>0.1188036589135511</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00647845111161035</v>
+        <v>0.006285279376014634</v>
       </c>
       <c r="D25" t="n">
-        <v>31.01524268844832</v>
+        <v>30.97122995046508</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03271069084937731</v>
+        <v>0.03309732419742849</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1077210986172392</v>
+        <v>0.1064393616730034</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1332007901910614</v>
+        <v>0.1311679561540991</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2318601867966585</v>
+        <v>0.228795958077564</v>
       </c>
     </row>
     <row r="26">
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1229849557856659</v>
+        <v>0.1220841068714277</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006104691195107123</v>
+        <v>0.006067088316176444</v>
       </c>
       <c r="D26" t="n">
-        <v>31.84669465832229</v>
+        <v>31.98943651107061</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03420637287696614</v>
+        <v>0.03476319447953307</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1109793702228082</v>
+        <v>0.1101491093588295</v>
       </c>
       <c r="G26" t="n">
-        <v>0.134990541348524</v>
+        <v>0.1340191043840256</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2343841981781743</v>
+        <v>0.2320764060354406</v>
       </c>
     </row>
     <row r="27">
@@ -997,25 +997,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1293952131760527</v>
+        <v>0.1285062555327081</v>
       </c>
       <c r="C27" t="n">
-        <v>0.005807337085421548</v>
+        <v>0.005750351078018348</v>
       </c>
       <c r="D27" t="n">
-        <v>32.10128645339148</v>
+        <v>32.31614189231452</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03514030670067056</v>
+        <v>0.03466395388419161</v>
       </c>
       <c r="F27" t="n">
-        <v>0.117993919839423</v>
+        <v>0.1172134284264973</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1407965065126831</v>
+        <v>0.1397990826389189</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2407944555685611</v>
+        <v>0.238498554696721</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1025,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1311854579586333</v>
+        <v>0.1307034897241006</v>
       </c>
       <c r="C28" t="n">
-        <v>0.005934526194959007</v>
+        <v>0.005672583267456475</v>
       </c>
       <c r="D28" t="n">
-        <v>31.39143688929453</v>
+        <v>31.69378520471996</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06214760782429639</v>
+        <v>0.06070533570692033</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1195352258102435</v>
+        <v>0.1195680472199546</v>
       </c>
       <c r="G28" t="n">
-        <v>0.142835690107023</v>
+        <v>0.1418389322282467</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2425847003511417</v>
+        <v>0.2406957888881135</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1053,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01316488972226798</v>
+        <v>0.005988692532679759</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0007613288916396197</v>
+        <v>0.0002545621745101684</v>
       </c>
       <c r="D29" t="n">
-        <v>2.496460847919775</v>
+        <v>1.551887414662227</v>
       </c>
       <c r="E29" t="n">
-        <v>0.003316006460320914</v>
+        <v>0.001235504602410451</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01166732989672211</v>
+        <v>0.005489497771230792</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01466244954781373</v>
+        <v>0.006487887294128722</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1245641321147764</v>
+        <v>0.1159809916966926</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year21final.xlsx
+++ b/hourly datasets/cap_gen_year21final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2293783550825633</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1099922991640129</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1002131562459241</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1245903538708641</v>
+        <v>0.3998321113716831</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.234582653034877</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2706669125350438</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1497308692574472</v>
+        <v>0.3546580651830682</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2597231684214601</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2254928663464289</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04037235188335056</v>
+        <v>0.3835052691910025</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1503646510473634</v>
+        <v>62</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2543400703543632</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0219042523036234</v>
+        <v>0.3780525305959329</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +574,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1318965514676363</v>
+        <v>62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2488873317592936</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +587,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01048225142366272</v>
+        <v>0.3737786080888844</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009690270228351216</v>
+        <v>0.004263628415475026</v>
       </c>
       <c r="D7" t="n">
-        <v>2.279231618169682</v>
+        <v>6.332977607648337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004674473351215604</v>
+        <v>0.006814983964800028</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008582127863249012</v>
+        <v>0.01960694040483692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01238237498407649</v>
+        <v>0.03633377972205896</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1204745505876756</v>
+        <v>62</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2446134092522451</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0047949996257823</v>
+        <v>0.3267964199012877</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -603,7 +626,10 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1147872987897952</v>
+        <v>62</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1976312210646484</v>
       </c>
     </row>
     <row r="9">
@@ -613,7 +639,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005354538264192019</v>
+        <v>0.3137320010625156</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -621,7 +647,10 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.1153468374282049</v>
+        <v>62</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1845668022258763</v>
       </c>
     </row>
     <row r="10">
@@ -631,25 +660,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004634699302963697</v>
+        <v>0.3155641175942054</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005019805384454752</v>
+        <v>0.007749613093499044</v>
       </c>
       <c r="D10" t="n">
-        <v>1.31814222373769</v>
+        <v>-3.802514608616305</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00101778462807955</v>
+        <v>0.001136653083413574</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003650114073445437</v>
+        <v>-0.05200218786505058</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005619284532481997</v>
+        <v>-0.02159418488571287</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1146269984669766</v>
+        <v>62</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1863989187575662</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +691,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02893992749805298</v>
+        <v>0.275856552973049</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -667,7 +699,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1389322266620658</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1466913541364097</v>
       </c>
     </row>
     <row r="12">
@@ -677,7 +712,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05439636376376</v>
+        <v>0.3033183914942105</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -685,7 +720,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1643886629277729</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1741531926575713</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +733,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07168763115979133</v>
+        <v>0.3249451473057498</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -703,7 +741,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1816799303238042</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1957799484691105</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +754,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08184471996025694</v>
+        <v>0.33526011735428</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -721,7 +762,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1918370191242698</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2060949185176407</v>
       </c>
     </row>
     <row r="15">
@@ -731,7 +775,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08722709666190667</v>
+        <v>0.3416190595054381</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -739,7 +783,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1972193958259195</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2124538606687988</v>
       </c>
     </row>
     <row r="16">
@@ -749,7 +796,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09199864996852229</v>
+        <v>0.345541746649804</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -757,7 +804,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.2019909491325352</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2163765478131648</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +817,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09562710807701701</v>
+        <v>0.3501945487184445</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -775,7 +825,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.2056194072410299</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2210293498818053</v>
       </c>
     </row>
     <row r="18">
@@ -785,24 +838,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1099922991640129</v>
+        <v>0.1291651988366393</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007475328656340139</v>
+        <v>0.007619305735355113</v>
       </c>
       <c r="D18" t="n">
-        <v>-23.43831166551434</v>
+        <v>-24.73445978354692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02516238180502941</v>
+        <v>0.02527601709925259</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1246656641882574</v>
+        <v>-0.1296483369246899</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09531893413976801</v>
+        <v>-0.09973675454682659</v>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -813,7 +869,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09716239785072142</v>
+        <v>0.3530540685439273</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -821,7 +877,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.2071546970147343</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.223888869707288</v>
       </c>
     </row>
     <row r="20">
@@ -831,7 +890,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09959519344057345</v>
+        <v>0.3554291022260423</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -839,7 +898,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2095874926045863</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.226263903389403</v>
       </c>
     </row>
     <row r="21">
@@ -849,25 +911,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1032827074198596</v>
+        <v>0.3593641509114508</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006113417648424865</v>
+        <v>0.006109613681463871</v>
       </c>
       <c r="D21" t="n">
-        <v>27.66357091915198</v>
+        <v>27.65083288520874</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0363941273807872</v>
+        <v>0.03633493841344335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09126727033739016</v>
+        <v>0.09121305687147457</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1152981445023289</v>
+        <v>0.11522899655138</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2132750065838725</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2301989520748115</v>
       </c>
     </row>
     <row r="22">
@@ -877,25 +942,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1068995960763939</v>
+        <v>0.364660084253472</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006169666318318684</v>
+        <v>0.006161679619130605</v>
       </c>
       <c r="D22" t="n">
-        <v>28.89223891325086</v>
+        <v>28.86482987870414</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03646600785838826</v>
+        <v>0.03645284875724884</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09476903545491545</v>
+        <v>0.09463648019382491</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1190301566978724</v>
+        <v>0.1188662432129889</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2168918952404068</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2354948854168327</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +973,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1127150527305676</v>
+        <v>0.3712951037146361</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +981,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2227073518945805</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2421299048779969</v>
       </c>
     </row>
     <row r="24">
@@ -923,7 +994,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1157665267859361</v>
+        <v>0.3764465504276476</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -931,7 +1002,10 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2257588259499489</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2472813515910084</v>
       </c>
     </row>
     <row r="25">
@@ -941,25 +1015,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1188036589135511</v>
+        <v>0.3817014818405133</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006285279376014634</v>
+        <v>0.006273078616181228</v>
       </c>
       <c r="D25" t="n">
-        <v>30.97122995046508</v>
+        <v>30.91986424252619</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03309732419742849</v>
+        <v>0.03307675106987333</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1064393616730034</v>
+        <v>0.1062039711360144</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1311679561540991</v>
+        <v>0.1308846609931038</v>
       </c>
       <c r="H25" t="n">
-        <v>0.228795958077564</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2525362830038741</v>
       </c>
     </row>
     <row r="26">
@@ -969,25 +1046,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1220841068714277</v>
+        <v>0.3850421265910695</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006067088316176444</v>
+        <v>0.006041315914222876</v>
       </c>
       <c r="D26" t="n">
-        <v>31.98943651107061</v>
+        <v>31.89569331956941</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03476319447953307</v>
+        <v>0.03473921688582488</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1101491093588295</v>
+        <v>0.1096711649245142</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1340191043840256</v>
+        <v>0.1334399716242095</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2320764060354406</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2558769277544303</v>
       </c>
     </row>
     <row r="27">
@@ -997,25 +1077,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1285062555327081</v>
+        <v>0.3910084237973294</v>
       </c>
       <c r="C27" t="n">
-        <v>0.005750351078018348</v>
+        <v>0.005703092398133489</v>
       </c>
       <c r="D27" t="n">
-        <v>32.31614189231452</v>
+        <v>32.14547065429137</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03466395388419161</v>
+        <v>0.03462005691147983</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1172134284264973</v>
+        <v>0.1162910370335043</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1397990826389189</v>
+        <v>0.1386911722936142</v>
       </c>
       <c r="H27" t="n">
-        <v>0.238498554696721</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2618432249606901</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1108,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1307034897241006</v>
+        <v>0.3959155439027396</v>
       </c>
       <c r="C28" t="n">
-        <v>0.005672583267456475</v>
+        <v>0.005570513501169698</v>
       </c>
       <c r="D28" t="n">
-        <v>31.69378520471996</v>
+        <v>31.46130808177064</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06070533570692033</v>
+        <v>0.06001054552342714</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1195680472199546</v>
+        <v>0.1180406057331037</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1418389322282467</v>
+        <v>0.1399108048964866</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2406957888881135</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2667503450661003</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1139,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005988692532679759</v>
+        <v>0.3526396027381042</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0002545621745101684</v>
+        <v>0.002145935305444426</v>
       </c>
       <c r="D29" t="n">
-        <v>1.551887414662227</v>
+        <v>-1.292441783611658</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001235504602410451</v>
+        <v>0.001822478778921551</v>
       </c>
       <c r="F29" t="n">
-        <v>0.005489497771230792</v>
+        <v>-0.003288838281432029</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006487887294128722</v>
+        <v>0.005131005946278361</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1159809916966926</v>
+        <v>62</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.223474403901465</v>
       </c>
     </row>
   </sheetData>
